--- a/reconcile/storage/output/ongoing/ongoing_battery_by_iso2_q.xlsx
+++ b/reconcile/storage/output/ongoing/ongoing_battery_by_iso2_q.xlsx
@@ -544,7 +544,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>337868.2764212993</v>
+        <v>337868.25</v>
       </c>
       <c r="D2" t="n">
         <v>16250000</v>
@@ -562,13 +562,13 @@
         <v>1666666.666666667</v>
       </c>
       <c r="I2" t="n">
-        <v>147392290.2494331</v>
+        <v>147392290</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>100750504.9611731</v>
+        <v>100750504.9402174</v>
       </c>
       <c r="L2" t="n">
         <v>14750000</v>
@@ -612,7 +612,7 @@
         <v>16250000</v>
       </c>
       <c r="E3" t="n">
-        <v>242333333.3333333</v>
+        <v>257914025.75</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>45792604.5670491</v>
+        <v>45792604.56521739</v>
       </c>
       <c r="L3" t="n">
         <v>14750000</v>
@@ -645,7 +645,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>485068679.1555439</v>
+        <v>485068679.1176471</v>
       </c>
       <c r="Q3" t="n">
         <v>1250000</v>
@@ -674,7 +674,7 @@
         <v>16250000</v>
       </c>
       <c r="E4" t="n">
-        <v>239000000</v>
+        <v>285742077.25</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -692,7 +692,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>45792604.5670491</v>
+        <v>45792604.56521739</v>
       </c>
       <c r="L4" t="n">
         <v>16833333.33333334</v>
@@ -707,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>485068679.1555439</v>
+        <v>485068679.1176471</v>
       </c>
       <c r="Q4" t="n">
         <v>1875000</v>
@@ -736,7 +736,7 @@
         <v>16250000</v>
       </c>
       <c r="E5" t="n">
-        <v>93333333.33333333</v>
+        <v>140075410.5833333</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -748,13 +748,13 @@
         <v>5000000</v>
       </c>
       <c r="I5" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>45792604.5670491</v>
+        <v>45792604.56521739</v>
       </c>
       <c r="L5" t="n">
         <v>14750000</v>
@@ -769,7 +769,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>485068679.1555439</v>
+        <v>485068679.1176471</v>
       </c>
       <c r="Q5" t="n">
         <v>1875000</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>381948773.2095491</v>
+        <v>381948773.1923077</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>16250000</v>
       </c>
       <c r="E6" t="n">
-        <v>20583333.33333333</v>
+        <v>67325410.58333333</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -810,13 +810,13 @@
         <v>5000000</v>
       </c>
       <c r="I6" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>96511354.5670491</v>
+        <v>96511354.56521739</v>
       </c>
       <c r="L6" t="n">
         <v>11250000</v>
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>485068679.1555439</v>
+        <v>485068679.1176471</v>
       </c>
       <c r="Q6" t="n">
         <v>1875000</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -860,7 +860,7 @@
         <v>5416666.666666667</v>
       </c>
       <c r="E7" t="n">
-        <v>46416666.66666667</v>
+        <v>93158743.91666666</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -872,13 +872,13 @@
         <v>201153846.1538461</v>
       </c>
       <c r="I7" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>197948854.5670491</v>
+        <v>197948854.5652174</v>
       </c>
       <c r="L7" t="n">
         <v>11250000</v>
@@ -893,7 +893,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>484756179.1555439</v>
+        <v>484756179.1176471</v>
       </c>
       <c r="Q7" t="n">
         <v>1875000</v>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>325600000</v>
+        <v>372342077.25</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -934,13 +934,13 @@
         <v>201153846.1538461</v>
       </c>
       <c r="I8" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="J8" t="n">
         <v>8333333.333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>197948854.5670491</v>
+        <v>197948854.5652174</v>
       </c>
       <c r="L8" t="n">
         <v>11250000</v>
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>326504119.4370292</v>
+        <v>326504119.4117647</v>
       </c>
       <c r="Q8" t="n">
         <v>1875000</v>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         <v>6445833.333333333</v>
       </c>
       <c r="E9" t="n">
-        <v>319608333.3333333</v>
+        <v>366350410.5833333</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -996,13 +996,13 @@
         <v>213653846.1538461</v>
       </c>
       <c r="I9" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="J9" t="n">
         <v>12500000</v>
       </c>
       <c r="K9" t="n">
-        <v>315595913.3905785</v>
+        <v>221478266.3299233</v>
       </c>
       <c r="L9" t="n">
         <v>6250000</v>
@@ -1014,7 +1014,7 @@
         <v>2500000</v>
       </c>
       <c r="O9" t="n">
-        <v>65041666.66666666</v>
+        <v>213030315.9047619</v>
       </c>
       <c r="P9" t="n">
         <v>22121212.12121212</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1046,7 +1046,7 @@
         <v>19337500</v>
       </c>
       <c r="E10" t="n">
-        <v>319608333.3333333</v>
+        <v>366350410.5833333</v>
       </c>
       <c r="F10" t="n">
         <v>145833333.3333333</v>
@@ -1058,13 +1058,13 @@
         <v>218237179.4871795</v>
       </c>
       <c r="I10" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="J10" t="n">
         <v>12500000</v>
       </c>
       <c r="K10" t="n">
-        <v>374419442.8023432</v>
+        <v>233242972.2122762</v>
       </c>
       <c r="L10" t="n">
         <v>6250000</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>85375000</v>
+        <v>307357973.8571428</v>
       </c>
       <c r="P10" t="n">
         <v>18181818.18181818</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>19337500</v>
       </c>
       <c r="E11" t="n">
-        <v>314747222.2222222</v>
+        <v>345908607.0555556</v>
       </c>
       <c r="F11" t="n">
         <v>437500000</v>
@@ -1120,13 +1120,13 @@
         <v>124134615.3846154</v>
       </c>
       <c r="I11" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="J11" t="n">
         <v>12500000</v>
       </c>
       <c r="K11" t="n">
-        <v>494169442.8023432</v>
+        <v>352992972.2122762</v>
       </c>
       <c r="L11" t="n">
         <v>6250000</v>
@@ -1138,7 +1138,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>85375000</v>
+        <v>307357973.8571428</v>
       </c>
       <c r="P11" t="n">
         <v>28181818.18181818</v>
@@ -1150,7 +1150,7 @@
         <v>19166666.66666667</v>
       </c>
       <c r="S11" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1182,13 +1182,13 @@
         <v>138750000</v>
       </c>
       <c r="I12" t="n">
-        <v>82376311.2829254</v>
+        <v>85866766.375</v>
       </c>
       <c r="J12" t="n">
         <v>12500000</v>
       </c>
       <c r="K12" t="n">
-        <v>508544442.8023432</v>
+        <v>367367972.2122762</v>
       </c>
       <c r="L12" t="n">
         <v>4166666.666666667</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>85375000</v>
+        <v>307357973.8571428</v>
       </c>
       <c r="P12" t="n">
         <v>48181818.18181818</v>
@@ -1212,7 +1212,7 @@
         <v>28750000</v>
       </c>
       <c r="S12" t="n">
-        <v>74256465.51724139</v>
+        <v>74256465.5</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1250,7 +1250,7 @@
         <v>12500000</v>
       </c>
       <c r="K13" t="n">
-        <v>629866857.1183881</v>
+        <v>488690386.5872762</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>85375000</v>
+        <v>307357973.8571428</v>
       </c>
       <c r="P13" t="n">
         <v>48181818.18181818</v>
@@ -1306,13 +1306,13 @@
         <v>344013157.8947369</v>
       </c>
       <c r="I14" t="n">
-        <v>388138487.8124514</v>
+        <v>388138487.8333333</v>
       </c>
       <c r="J14" t="n">
         <v>12500000</v>
       </c>
       <c r="K14" t="n">
-        <v>629866857.1183881</v>
+        <v>488690386.5872762</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1324,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>85375000</v>
+        <v>307357973.8571428</v>
       </c>
       <c r="P14" t="n">
         <v>48181818.18181818</v>
@@ -1368,13 +1368,13 @@
         <v>344013157.8947369</v>
       </c>
       <c r="I15" t="n">
-        <v>582207731.7186772</v>
+        <v>582207731.75</v>
       </c>
       <c r="J15" t="n">
         <v>12500000</v>
       </c>
       <c r="K15" t="n">
-        <v>629866857.1183881</v>
+        <v>488690386.5872762</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>85375000</v>
+        <v>307357973.8571428</v>
       </c>
       <c r="P15" t="n">
         <v>48181818.18181818</v>
@@ -1421,7 +1421,7 @@
         <v>8333.333333333334</v>
       </c>
       <c r="F16" t="n">
-        <v>746375586.953763</v>
+        <v>746375586.909091</v>
       </c>
       <c r="G16" t="n">
         <v>96750000</v>
@@ -1430,13 +1430,13 @@
         <v>344013157.8947369</v>
       </c>
       <c r="I16" t="n">
-        <v>611174693.0960619</v>
+        <v>611174693.125</v>
       </c>
       <c r="J16" t="n">
         <v>4166666.666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>629866857.1183881</v>
+        <v>488690386.5872762</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1448,10 +1448,10 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>44708333.33333333</v>
+        <v>118702657.9523809</v>
       </c>
       <c r="P16" t="n">
-        <v>50059166.5821158</v>
+        <v>50059166.55681818</v>
       </c>
       <c r="Q16" t="n">
         <v>14875000</v>
@@ -1483,7 +1483,7 @@
         <v>48333333.33333334</v>
       </c>
       <c r="F17" t="n">
-        <v>746375586.953763</v>
+        <v>746375586.909091</v>
       </c>
       <c r="G17" t="n">
         <v>96750000</v>
@@ -1492,13 +1492,13 @@
         <v>331513157.8947369</v>
       </c>
       <c r="I17" t="n">
-        <v>611174693.0960619</v>
+        <v>611174693.125</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>497900954.0736887</v>
+        <v>356724483.543798</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>50059166.5821158</v>
+        <v>50059166.55681818</v>
       </c>
       <c r="Q17" t="n">
         <v>14875000</v>
@@ -1545,7 +1545,7 @@
         <v>72500000</v>
       </c>
       <c r="F18" t="n">
-        <v>600542253.6204296</v>
+        <v>600542253.5757576</v>
       </c>
       <c r="G18" t="n">
         <v>130083333.3333333</v>
@@ -1554,13 +1554,13 @@
         <v>325263157.8947369</v>
       </c>
       <c r="I18" t="n">
-        <v>611174693.0960619</v>
+        <v>611174693.125</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>431918002.551339</v>
+        <v>290741532.0220588</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>50059166.5821158</v>
+        <v>50059166.55681818</v>
       </c>
       <c r="Q18" t="n">
         <v>14875000</v>
@@ -1584,7 +1584,7 @@
         <v>53750000</v>
       </c>
       <c r="S18" t="n">
-        <v>362950058.0720093</v>
+        <v>327778579</v>
       </c>
       <c r="T18" t="n">
         <v>153750000</v>
@@ -1607,7 +1607,7 @@
         <v>21666666.66666666</v>
       </c>
       <c r="F19" t="n">
-        <v>281602859.6810356</v>
+        <v>281602859.6363636</v>
       </c>
       <c r="G19" t="n">
         <v>296750000</v>
@@ -1616,13 +1616,13 @@
         <v>263842105.2631579</v>
       </c>
       <c r="I19" t="n">
-        <v>611174693.0960619</v>
+        <v>611174693.125</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>920501335.8846724</v>
+        <v>779324865.3553922</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>40059166.5821158</v>
+        <v>40059166.55681818</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1646,7 +1646,7 @@
         <v>34583333.33333334</v>
       </c>
       <c r="S19" t="n">
-        <v>362950058.0720093</v>
+        <v>327778579</v>
       </c>
       <c r="T19" t="n">
         <v>153750000</v>
@@ -1669,7 +1669,7 @@
         <v>28504166.66666666</v>
       </c>
       <c r="F20" t="n">
-        <v>267966496.044672</v>
+        <v>267966496</v>
       </c>
       <c r="G20" t="n">
         <v>265583333.3333333</v>
@@ -1678,13 +1678,13 @@
         <v>7000000</v>
       </c>
       <c r="I20" t="n">
-        <v>611174693.0960619</v>
+        <v>611174693.125</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1151469473.139574</v>
+        <v>1057351826.139706</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>7937954.460903681</v>
+        <v>7937954.435606061</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>25000000</v>
       </c>
       <c r="S20" t="n">
-        <v>362950058.0720093</v>
+        <v>327778579</v>
       </c>
       <c r="T20" t="n">
         <v>153750000</v>
@@ -1731,7 +1731,7 @@
         <v>30337500</v>
       </c>
       <c r="F21" t="n">
-        <v>267966496.044672</v>
+        <v>267966496</v>
       </c>
       <c r="G21" t="n">
         <v>300000000</v>
@@ -1740,7 +1740,7 @@
         <v>7000000</v>
       </c>
       <c r="I21" t="n">
-        <v>611174693.0960619</v>
+        <v>611174693.125</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1877348.40029762</v>
+        <v>1877348.375</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -1770,7 +1770,7 @@
         <v>25000000</v>
       </c>
       <c r="S21" t="n">
-        <v>362950058.0720093</v>
+        <v>327778579</v>
       </c>
       <c r="T21" t="n">
         <v>153750000</v>
